--- a/consent_forms/039_facility_upgrade_observation_consent_form--consent_forms.xlsx
+++ b/consent_forms/039_facility_upgrade_observation_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>facility_upgrade_observation_consent_form_1</t>
+          <t>facility_upgrade_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Facility Upgrades</t>
+          <t>Facility Upgrade Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>facility_upgrade_observation_consent_form_2</t>
+          <t>facility_upgrade_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Facility Upgrades</t>
+          <t>Facility Upgrade Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>facility_upgrade_observation_consent_form_3</t>
+          <t>upgrade_reason</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Facility Upgrades</t>
+          <t>Upgrade Reason</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>facility_upgrade_observation_consent_form_4</t>
+          <t>expected_completion_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Facility Upgrades</t>
+          <t>Expected Completion Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>facility_upgrade_observation_consent_form_5</t>
+          <t>preferred_upgrade_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Facility Upgrades</t>
+          <t>Preferred Time for Upgrade</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>facility_upgrade_observation_consent_form_6</t>
+          <t>upgrade_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Facility Upgrades</t>
+          <t>Upgrade Location</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,21 +653,136 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>facility_upgrade_observation_consent_form_7</t>
+          <t>consent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Facility Upgrades</t>
+          <t>Consent</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>facility_upgrade_observation_consent_form_8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Is There Anything Else You Would Like to Comment?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>facility_upgrade_observation_consent_form_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Facility Upgrade Observation Consent Form 9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>facility_upgrade_observation_consent_form_10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Facility Upgrade Observation Consent Form 10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>facility_upgrade_observation_consent_form_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Facility Upgrade Observation Consent Form 11</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>facility_upgrade_observation_consent_form_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Facility Upgrade Observation Consent Form 12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -684,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -712,68 +827,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>facility_upgrade_observation_consent_form_1_choices</t>
+          <t>facility_upgrade_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>facility_upgrade_observation_consent_form_1_choices</t>
+          <t>facility_upgrade_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>facility_upgrade_observation_consent_form_2_choices</t>
+          <t>upgrade_location_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>facility_upgrade_observation_consent_form_2_choices</t>
+          <t>upgrade_location_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>consent_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>consent_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
